--- a/Sanitized_Data/samples/对账单.xlsx
+++ b/Sanitized_Data/samples/对账单.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31310000E12345678X</t>
+          <t>91310000MA1FL1XX0G</t>
         </is>
       </c>
       <c r="D5" t="n">
